--- a/outputs/daily/hr_rankings_2026-07-18.xlsx
+++ b/outputs/daily/hr_rankings_2026-07-18.xlsx
@@ -784,7 +784,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>77</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -808,7 +808,7 @@
         <v>68.2</v>
       </c>
       <c r="R2" t="n">
-        <v>57.6</v>
+        <v>57.1</v>
       </c>
       <c r="S2" t="n">
         <v>94.90000000000001</v>
@@ -999,7 +999,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>84</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1064,7 +1064,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>68.5</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -1088,7 +1088,7 @@
         <v>68.2</v>
       </c>
       <c r="R3" t="n">
-        <v>57.6</v>
+        <v>57.1</v>
       </c>
       <c r="S3" t="n">
         <v>52.4</v>
@@ -1279,7 +1279,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>84</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1924,7 +1924,7 @@
         <v>67.59999999999999</v>
       </c>
       <c r="R6" t="n">
-        <v>57.6</v>
+        <v>57.1</v>
       </c>
       <c r="S6" t="n">
         <v>96.59999999999999</v>
@@ -2115,7 +2115,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>84</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2407,52 +2407,52 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>542303</t>
+          <t>682985</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Marcell Ozuna</t>
+          <t>Riley Greene</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-07-18T23:10:00Z</t>
+          <t>2026-07-19T02:07:00Z</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Logan Allen</t>
+          <t>Grayson Rodriguez</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>671106</t>
+          <t>680570</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L8" t="n">
@@ -2470,61 +2470,65 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>42</v>
+        <v>60.2</v>
       </c>
       <c r="Q8" t="n">
-        <v>68.2</v>
+        <v>60.5</v>
       </c>
       <c r="R8" t="n">
-        <v>57.6</v>
+        <v>28.2</v>
       </c>
       <c r="S8" t="n">
-        <v>76.2</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="T8" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="U8" t="n">
-        <v>54.7</v>
+        <v>16.1</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="Z8" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr"/>
@@ -2541,142 +2545,134 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 5/22, 0 HR</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 15.5% barrel, 5.4 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.7% barrel, 4.0 HR allowed</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>9.75</t>
+          <t>14.72</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>40.54</t>
+          <t>48.51</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>89.76</t>
+          <t>90.95</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>100.2738</t>
+          <t>102.8018</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>0.4207</t>
+          <t>0.4833</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>0.1915</t>
+          <t>0.2277</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>0.3253</t>
+          <t>0.3551</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>73.39</t>
+          <t>75.67</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>36.43</t>
+          <t>58.67</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>40.03</t>
+          <t>39.82</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>31.2</t>
+          <t>32.47</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>11.9</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>0.1414</t>
+          <t>0.1937</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>15.47</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>49.4</t>
+          <t>51.0</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>92.38</t>
+          <t>91.4</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>0.428</t>
+          <t>0.531</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
-          <t>0.1845</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>32.53</t>
-        </is>
-      </c>
-      <c r="BG8" t="inlineStr">
-        <is>
-          <t>L To R</t>
-        </is>
-      </c>
-      <c r="BH8" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
+          <t>28.8</t>
+        </is>
+      </c>
+      <c r="BG8" t="inlineStr"/>
+      <c r="BH8" t="inlineStr"/>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>Progressive Field</t>
+          <t>Angel Stadium</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr"/>
@@ -2687,56 +2683,56 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>682985</t>
+          <t>542303</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Riley Greene</t>
+          <t>Marcell Ozuna</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-07-19T02:07:00Z</t>
+          <t>2026-07-18T23:10:00Z</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Grayson Rodriguez</t>
+          <t>Logan Allen</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>680570</t>
+          <t>671106</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>59.3</v>
+        <v>59.2</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -2750,65 +2746,61 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>60.2</v>
+        <v>42</v>
       </c>
       <c r="Q9" t="n">
-        <v>60.5</v>
+        <v>68.2</v>
       </c>
       <c r="R9" t="n">
-        <v>28.2</v>
+        <v>57.1</v>
       </c>
       <c r="S9" t="n">
-        <v>90.40000000000001</v>
+        <v>76.2</v>
       </c>
       <c r="T9" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="U9" t="n">
-        <v>16.1</v>
+        <v>54.7</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr"/>
@@ -2825,134 +2817,142 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/22, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.7% barrel, 4.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 15.5% barrel, 5.4 HR allowed</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>14.72</t>
+          <t>9.75</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>48.51</t>
+          <t>40.54</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>90.95</t>
+          <t>89.76</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>102.8018</t>
+          <t>100.2738</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>0.4833</t>
+          <t>0.4207</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>0.2277</t>
+          <t>0.1915</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>0.3551</t>
+          <t>0.3253</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>75.67</t>
+          <t>73.39</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>58.67</t>
+          <t>36.43</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>39.82</t>
+          <t>40.03</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>32.47</t>
+          <t>31.2</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>11.9</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>0.1937</t>
+          <t>0.1414</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>15.47</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>51.0</t>
+          <t>49.4</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>91.4</t>
+          <t>92.38</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>0.531</t>
+          <t>0.428</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>0.1845</t>
         </is>
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>28.8</t>
-        </is>
-      </c>
-      <c r="BG9" t="inlineStr"/>
-      <c r="BH9" t="inlineStr"/>
+          <t>32.53</t>
+        </is>
+      </c>
+      <c r="BG9" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH9" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>Angel Stadium</t>
+          <t>Progressive Field</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr"/>
@@ -3564,7 +3564,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>58</v>
+        <v>57.9</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -3588,7 +3588,7 @@
         <v>68.2</v>
       </c>
       <c r="R12" t="n">
-        <v>57.6</v>
+        <v>57.1</v>
       </c>
       <c r="S12" t="n">
         <v>86.40000000000001</v>
@@ -3779,7 +3779,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>84</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -3868,7 +3868,7 @@
         <v>68.2</v>
       </c>
       <c r="R13" t="n">
-        <v>57.6</v>
+        <v>57.1</v>
       </c>
       <c r="S13" t="n">
         <v>64.3</v>
@@ -4059,7 +4059,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>84</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -5516,7 +5516,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>53.2</v>
+        <v>53.1</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -5540,7 +5540,7 @@
         <v>68.2</v>
       </c>
       <c r="R19" t="n">
-        <v>57.6</v>
+        <v>57.1</v>
       </c>
       <c r="S19" t="n">
         <v>100</v>
@@ -5731,7 +5731,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>84</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -6904,7 +6904,7 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>51.5</v>
+        <v>51.4</v>
       </c>
       <c r="M24" t="inlineStr">
         <is>
@@ -6928,7 +6928,7 @@
         <v>34.4</v>
       </c>
       <c r="R24" t="n">
-        <v>57.6</v>
+        <v>57.1</v>
       </c>
       <c r="S24" t="n">
         <v>94.90000000000001</v>
@@ -7119,7 +7119,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>84</t>
         </is>
       </c>
       <c r="BI24" t="inlineStr">
@@ -7460,7 +7460,7 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>50.8</v>
+        <v>50.7</v>
       </c>
       <c r="M26" t="inlineStr">
         <is>
@@ -7484,7 +7484,7 @@
         <v>34.4</v>
       </c>
       <c r="R26" t="n">
-        <v>57.6</v>
+        <v>57.1</v>
       </c>
       <c r="S26" t="n">
         <v>96.59999999999999</v>
@@ -7675,7 +7675,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>84</t>
         </is>
       </c>
       <c r="BI26" t="inlineStr">
@@ -9124,7 +9124,7 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>48.5</v>
+        <v>48.4</v>
       </c>
       <c r="M32" t="inlineStr">
         <is>
@@ -9148,7 +9148,7 @@
         <v>67.59999999999999</v>
       </c>
       <c r="R32" t="n">
-        <v>57.6</v>
+        <v>57.1</v>
       </c>
       <c r="S32" t="n">
         <v>93.2</v>
@@ -9339,7 +9339,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>84</t>
         </is>
       </c>
       <c r="BI32" t="inlineStr">
@@ -11352,7 +11352,7 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>44.9</v>
+        <v>44.8</v>
       </c>
       <c r="M40" t="inlineStr">
         <is>
@@ -11376,7 +11376,7 @@
         <v>33.9</v>
       </c>
       <c r="R40" t="n">
-        <v>57.6</v>
+        <v>57.1</v>
       </c>
       <c r="S40" t="n">
         <v>100</v>
@@ -11567,7 +11567,7 @@
       </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>84</t>
         </is>
       </c>
       <c r="BI40" t="inlineStr">
@@ -12135,32 +12135,32 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>682177</t>
+          <t>811965</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Daniel Schneemann</t>
+          <t>Joshua Kuroda-Grauer</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>ATH</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>WSH</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-07-18T23:10:00Z</t>
+          <t>2026-07-19T02:05:00Z</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -12170,17 +12170,17 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Mason Montgomery</t>
+          <t>Zack Littell</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>682254</t>
+          <t>641793</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L43" t="n">
@@ -12198,61 +12198,65 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>No major boost</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P43" t="n">
-        <v>32.5</v>
+        <v>16.1</v>
       </c>
       <c r="Q43" t="n">
-        <v>34.4</v>
+        <v>67.7</v>
       </c>
       <c r="R43" t="n">
-        <v>57.6</v>
+        <v>30.9</v>
       </c>
       <c r="S43" t="n">
-        <v>86.40000000000001</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="T43" t="n">
         <v>50</v>
       </c>
       <c r="U43" t="n">
-        <v>3.4</v>
+        <v>45</v>
       </c>
       <c r="V43" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W43" t="inlineStr">
+      <c r="Z43" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X43" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y43" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD43" t="inlineStr"/>
@@ -12269,12 +12273,12 @@
       </c>
       <c r="AH43" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AI43" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ43" t="inlineStr">
@@ -12284,127 +12288,119 @@
       </c>
       <c r="AK43" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/21, 0 HR</t>
+          <t>Contact streak: 12/27 over last 7 games</t>
         </is>
       </c>
       <c r="AL43" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 9.3% barrel, 4.6 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 10.9% barrel, 26.9 HR allowed</t>
         </is>
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN43" t="inlineStr">
         <is>
-          <t>9.05</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>39.32</t>
+          <t>38.1</t>
         </is>
       </c>
       <c r="AP43" t="inlineStr">
         <is>
-          <t>88.27</t>
+          <t>89.1</t>
         </is>
       </c>
       <c r="AQ43" t="inlineStr">
         <is>
-          <t>99.0368</t>
+          <t>99.1611</t>
         </is>
       </c>
       <c r="AR43" t="inlineStr">
         <is>
-          <t>0.3723</t>
+          <t>0.392</t>
         </is>
       </c>
       <c r="AS43" t="inlineStr">
         <is>
-          <t>0.1527</t>
+          <t>0.068</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr">
         <is>
-          <t>0.2907</t>
+          <t>0.319</t>
         </is>
       </c>
       <c r="AU43" t="inlineStr">
         <is>
-          <t>71.11</t>
+          <t>68.6</t>
         </is>
       </c>
       <c r="AV43" t="inlineStr">
         <is>
-          <t>11.86</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>46.37</t>
+          <t>39.5</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>29.02</t>
+          <t>11.6</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr">
         <is>
-          <t>7.8</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>0.1298</t>
+          <t>0.122</t>
         </is>
       </c>
       <c r="BA43" t="inlineStr">
         <is>
-          <t>9.33</t>
+          <t>10.95</t>
         </is>
       </c>
       <c r="BB43" t="inlineStr">
         <is>
-          <t>40.19</t>
+          <t>44.12</t>
         </is>
       </c>
       <c r="BC43" t="inlineStr">
         <is>
-          <t>87.83</t>
+          <t>91.39</t>
         </is>
       </c>
       <c r="BD43" t="inlineStr">
         <is>
-          <t>0.3499</t>
+          <t>0.5154</t>
         </is>
       </c>
       <c r="BE43" t="inlineStr">
         <is>
-          <t>0.1321</t>
+          <t>0.2341</t>
         </is>
       </c>
       <c r="BF43" t="inlineStr">
         <is>
-          <t>22.01</t>
-        </is>
-      </c>
-      <c r="BG43" t="inlineStr">
-        <is>
-          <t>L To R</t>
-        </is>
-      </c>
-      <c r="BH43" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
+          <t>32.0</t>
+        </is>
+      </c>
+      <c r="BG43" t="inlineStr"/>
+      <c r="BH43" t="inlineStr"/>
       <c r="BI43" t="inlineStr">
         <is>
-          <t>Progressive Field</t>
+          <t>Sutter Health Park</t>
         </is>
       </c>
       <c r="BJ43" t="inlineStr"/>
@@ -12415,32 +12411,32 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>811965</t>
+          <t>682177</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Joshua Kuroda-Grauer</t>
+          <t>Daniel Schneemann</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>ATH</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>WSH</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-07-19T02:05:00Z</t>
+          <t>2026-07-18T23:10:00Z</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -12450,21 +12446,21 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Zack Littell</t>
+          <t>Mason Montgomery</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>641793</t>
+          <t>682254</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L44" t="n">
-        <v>44.4</v>
+        <v>44.3</v>
       </c>
       <c r="M44" t="inlineStr">
         <is>
@@ -12478,65 +12474,61 @@
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P44" t="n">
-        <v>16.1</v>
+        <v>32.5</v>
       </c>
       <c r="Q44" t="n">
-        <v>67.7</v>
+        <v>34.4</v>
       </c>
       <c r="R44" t="n">
-        <v>30.9</v>
+        <v>57.1</v>
       </c>
       <c r="S44" t="n">
-        <v>81.90000000000001</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T44" t="n">
         <v>50</v>
       </c>
       <c r="U44" t="n">
-        <v>45</v>
+        <v>3.4</v>
       </c>
       <c r="V44" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W44" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X44" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y44" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr"/>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD44" t="inlineStr"/>
@@ -12553,12 +12545,12 @@
       </c>
       <c r="AH44" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI44" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ44" t="inlineStr">
@@ -12568,119 +12560,127 @@
       </c>
       <c r="AK44" t="inlineStr">
         <is>
-          <t>Contact streak: 12/27 over last 7 games</t>
+          <t>Last 7 games: 3/21, 0 HR</t>
         </is>
       </c>
       <c r="AL44" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 10.9% barrel, 26.9 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 9.3% barrel, 4.6 HR allowed</t>
         </is>
       </c>
       <c r="AM44" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN44" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>9.05</t>
         </is>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>39.32</t>
         </is>
       </c>
       <c r="AP44" t="inlineStr">
         <is>
-          <t>89.1</t>
+          <t>88.27</t>
         </is>
       </c>
       <c r="AQ44" t="inlineStr">
         <is>
-          <t>99.1611</t>
+          <t>99.0368</t>
         </is>
       </c>
       <c r="AR44" t="inlineStr">
         <is>
-          <t>0.392</t>
+          <t>0.3723</t>
         </is>
       </c>
       <c r="AS44" t="inlineStr">
         <is>
-          <t>0.068</t>
+          <t>0.1527</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr">
         <is>
-          <t>0.319</t>
+          <t>0.2907</t>
         </is>
       </c>
       <c r="AU44" t="inlineStr">
         <is>
-          <t>68.6</t>
+          <t>71.11</t>
         </is>
       </c>
       <c r="AV44" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>11.86</t>
         </is>
       </c>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>39.5</t>
+          <t>46.37</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>11.6</t>
+          <t>29.02</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.8</t>
         </is>
       </c>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>0.122</t>
+          <t>0.1298</t>
         </is>
       </c>
       <c r="BA44" t="inlineStr">
         <is>
-          <t>10.95</t>
+          <t>9.33</t>
         </is>
       </c>
       <c r="BB44" t="inlineStr">
         <is>
-          <t>44.12</t>
+          <t>40.19</t>
         </is>
       </c>
       <c r="BC44" t="inlineStr">
         <is>
-          <t>91.39</t>
+          <t>87.83</t>
         </is>
       </c>
       <c r="BD44" t="inlineStr">
         <is>
-          <t>0.5154</t>
+          <t>0.3499</t>
         </is>
       </c>
       <c r="BE44" t="inlineStr">
         <is>
-          <t>0.2341</t>
+          <t>0.1321</t>
         </is>
       </c>
       <c r="BF44" t="inlineStr">
         <is>
-          <t>32.0</t>
-        </is>
-      </c>
-      <c r="BG44" t="inlineStr"/>
-      <c r="BH44" t="inlineStr"/>
+          <t>22.01</t>
+        </is>
+      </c>
+      <c r="BG44" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH44" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
       <c r="BI44" t="inlineStr">
         <is>
-          <t>Sutter Health Park</t>
+          <t>Progressive Field</t>
         </is>
       </c>
       <c r="BJ44" t="inlineStr"/>
@@ -12740,7 +12740,7 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>43.9</v>
+        <v>43.8</v>
       </c>
       <c r="M45" t="inlineStr">
         <is>
@@ -12764,7 +12764,7 @@
         <v>68.2</v>
       </c>
       <c r="R45" t="n">
-        <v>57.6</v>
+        <v>57.1</v>
       </c>
       <c r="S45" t="n">
         <v>44.8</v>
@@ -12955,7 +12955,7 @@
       </c>
       <c r="BH45" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>84</t>
         </is>
       </c>
       <c r="BI45" t="inlineStr">
@@ -13020,7 +13020,7 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>42.8</v>
+        <v>42.7</v>
       </c>
       <c r="M46" t="inlineStr">
         <is>
@@ -13044,7 +13044,7 @@
         <v>34.4</v>
       </c>
       <c r="R46" t="n">
-        <v>57.6</v>
+        <v>57.1</v>
       </c>
       <c r="S46" t="n">
         <v>76.2</v>
@@ -13235,7 +13235,7 @@
       </c>
       <c r="BH46" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>84</t>
         </is>
       </c>
       <c r="BI46" t="inlineStr">
@@ -14712,7 +14712,7 @@
         <v>34.4</v>
       </c>
       <c r="R52" t="n">
-        <v>57.6</v>
+        <v>57.1</v>
       </c>
       <c r="S52" t="n">
         <v>93.2</v>
@@ -14903,7 +14903,7 @@
       </c>
       <c r="BH52" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>84</t>
         </is>
       </c>
       <c r="BI52" t="inlineStr">
@@ -15796,7 +15796,7 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>40.4</v>
+        <v>40.3</v>
       </c>
       <c r="M56" t="inlineStr">
         <is>
@@ -15820,7 +15820,7 @@
         <v>34.4</v>
       </c>
       <c r="R56" t="n">
-        <v>57.6</v>
+        <v>57.1</v>
       </c>
       <c r="S56" t="n">
         <v>52.4</v>
@@ -16011,7 +16011,7 @@
       </c>
       <c r="BH56" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>84</t>
         </is>
       </c>
       <c r="BI56" t="inlineStr">
@@ -18852,7 +18852,7 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>34.3</v>
+        <v>34.2</v>
       </c>
       <c r="M67" t="inlineStr">
         <is>
@@ -18876,7 +18876,7 @@
         <v>34.4</v>
       </c>
       <c r="R67" t="n">
-        <v>57.6</v>
+        <v>57.1</v>
       </c>
       <c r="S67" t="n">
         <v>64.3</v>
@@ -19067,7 +19067,7 @@
       </c>
       <c r="BH67" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>84</t>
         </is>
       </c>
       <c r="BI67" t="inlineStr">
@@ -20244,7 +20244,7 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>30.1</v>
+        <v>30</v>
       </c>
       <c r="M72" t="inlineStr">
         <is>
@@ -20268,7 +20268,7 @@
         <v>34.4</v>
       </c>
       <c r="R72" t="n">
-        <v>57.6</v>
+        <v>57.1</v>
       </c>
       <c r="S72" t="n">
         <v>44.8</v>
@@ -20459,7 +20459,7 @@
       </c>
       <c r="BH72" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>84</t>
         </is>
       </c>
       <c r="BI72" t="inlineStr">
@@ -21126,7 +21126,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>77</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -21150,7 +21150,7 @@
         <v>68.2</v>
       </c>
       <c r="R2" t="n">
-        <v>57.6</v>
+        <v>57.1</v>
       </c>
       <c r="S2" t="n">
         <v>94.90000000000001</v>
@@ -21341,7 +21341,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>84</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -21406,7 +21406,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>68.5</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -21430,7 +21430,7 @@
         <v>68.2</v>
       </c>
       <c r="R3" t="n">
-        <v>57.6</v>
+        <v>57.1</v>
       </c>
       <c r="S3" t="n">
         <v>52.4</v>
@@ -21621,7 +21621,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>84</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -22266,7 +22266,7 @@
         <v>67.59999999999999</v>
       </c>
       <c r="R6" t="n">
-        <v>57.6</v>
+        <v>57.1</v>
       </c>
       <c r="S6" t="n">
         <v>96.59999999999999</v>
@@ -22457,7 +22457,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>84</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -22749,52 +22749,52 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>542303</t>
+          <t>682985</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Marcell Ozuna</t>
+          <t>Riley Greene</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-07-18T23:10:00Z</t>
+          <t>2026-07-19T02:07:00Z</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Logan Allen</t>
+          <t>Grayson Rodriguez</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>671106</t>
+          <t>680570</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L8" t="n">
@@ -22812,61 +22812,65 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>42</v>
+        <v>60.2</v>
       </c>
       <c r="Q8" t="n">
-        <v>68.2</v>
+        <v>60.5</v>
       </c>
       <c r="R8" t="n">
-        <v>57.6</v>
+        <v>28.2</v>
       </c>
       <c r="S8" t="n">
-        <v>76.2</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="T8" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="U8" t="n">
-        <v>54.7</v>
+        <v>16.1</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="Z8" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr"/>
@@ -22883,142 +22887,134 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 5/22, 0 HR</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 15.5% barrel, 5.4 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.7% barrel, 4.0 HR allowed</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>9.75</t>
+          <t>14.72</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>40.54</t>
+          <t>48.51</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>89.76</t>
+          <t>90.95</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>100.2738</t>
+          <t>102.8018</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>0.4207</t>
+          <t>0.4833</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>0.1915</t>
+          <t>0.2277</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>0.3253</t>
+          <t>0.3551</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>73.39</t>
+          <t>75.67</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>36.43</t>
+          <t>58.67</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>40.03</t>
+          <t>39.82</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>31.2</t>
+          <t>32.47</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>11.9</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>0.1414</t>
+          <t>0.1937</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>15.47</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>49.4</t>
+          <t>51.0</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>92.38</t>
+          <t>91.4</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>0.428</t>
+          <t>0.531</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
-          <t>0.1845</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>32.53</t>
-        </is>
-      </c>
-      <c r="BG8" t="inlineStr">
-        <is>
-          <t>L To R</t>
-        </is>
-      </c>
-      <c r="BH8" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
+          <t>28.8</t>
+        </is>
+      </c>
+      <c r="BG8" t="inlineStr"/>
+      <c r="BH8" t="inlineStr"/>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>Progressive Field</t>
+          <t>Angel Stadium</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr"/>
@@ -23029,56 +23025,56 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>682985</t>
+          <t>542303</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Riley Greene</t>
+          <t>Marcell Ozuna</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-07-19T02:07:00Z</t>
+          <t>2026-07-18T23:10:00Z</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Grayson Rodriguez</t>
+          <t>Logan Allen</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>680570</t>
+          <t>671106</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>59.3</v>
+        <v>59.2</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -23092,65 +23088,61 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>60.2</v>
+        <v>42</v>
       </c>
       <c r="Q9" t="n">
-        <v>60.5</v>
+        <v>68.2</v>
       </c>
       <c r="R9" t="n">
-        <v>28.2</v>
+        <v>57.1</v>
       </c>
       <c r="S9" t="n">
-        <v>90.40000000000001</v>
+        <v>76.2</v>
       </c>
       <c r="T9" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="U9" t="n">
-        <v>16.1</v>
+        <v>54.7</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr"/>
@@ -23167,134 +23159,142 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/22, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.7% barrel, 4.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 15.5% barrel, 5.4 HR allowed</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>14.72</t>
+          <t>9.75</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>48.51</t>
+          <t>40.54</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>90.95</t>
+          <t>89.76</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>102.8018</t>
+          <t>100.2738</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>0.4833</t>
+          <t>0.4207</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>0.2277</t>
+          <t>0.1915</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>0.3551</t>
+          <t>0.3253</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>75.67</t>
+          <t>73.39</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>58.67</t>
+          <t>36.43</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>39.82</t>
+          <t>40.03</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>32.47</t>
+          <t>31.2</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>11.9</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>0.1937</t>
+          <t>0.1414</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>15.47</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>51.0</t>
+          <t>49.4</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>91.4</t>
+          <t>92.38</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>0.531</t>
+          <t>0.428</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>0.1845</t>
         </is>
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>28.8</t>
-        </is>
-      </c>
-      <c r="BG9" t="inlineStr"/>
-      <c r="BH9" t="inlineStr"/>
+          <t>32.53</t>
+        </is>
+      </c>
+      <c r="BG9" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH9" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>Angel Stadium</t>
+          <t>Progressive Field</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr"/>
@@ -23906,7 +23906,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>58</v>
+        <v>57.9</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -23930,7 +23930,7 @@
         <v>68.2</v>
       </c>
       <c r="R12" t="n">
-        <v>57.6</v>
+        <v>57.1</v>
       </c>
       <c r="S12" t="n">
         <v>86.40000000000001</v>
@@ -24121,7 +24121,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>84</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -24210,7 +24210,7 @@
         <v>68.2</v>
       </c>
       <c r="R13" t="n">
-        <v>57.6</v>
+        <v>57.1</v>
       </c>
       <c r="S13" t="n">
         <v>64.3</v>
@@ -24401,7 +24401,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>84</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -25858,7 +25858,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>53.2</v>
+        <v>53.1</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -25882,7 +25882,7 @@
         <v>68.2</v>
       </c>
       <c r="R19" t="n">
-        <v>57.6</v>
+        <v>57.1</v>
       </c>
       <c r="S19" t="n">
         <v>100</v>
@@ -26073,7 +26073,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>84</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">

--- a/outputs/daily/hr_rankings_2026-07-18.xlsx
+++ b/outputs/daily/hr_rankings_2026-07-18.xlsx
@@ -826,34 +826,30 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -3078,34 +3074,30 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -5058,34 +5050,30 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -5900,28 +5888,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="W20" t="inlineStr"/>
-      <c r="X20" t="inlineStr"/>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="Y20" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB20" t="inlineStr"/>
       <c r="AC20" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -8698,34 +8690,30 @@
       </c>
       <c r="W30" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X30" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y30" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB30" t="inlineStr"/>
       <c r="AC30" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -10950,34 +10938,30 @@
       </c>
       <c r="W38" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X38" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y38" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 5 vs RotoWire 7</t>
-        </is>
-      </c>
+      <c r="AB38" t="inlineStr"/>
       <c r="AC38" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -12638,34 +12622,30 @@
       </c>
       <c r="W44" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X44" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y44" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 9 vs RotoWire 5</t>
-        </is>
-      </c>
+      <c r="AB44" t="inlineStr"/>
       <c r="AC44" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -14602,34 +14582,30 @@
       </c>
       <c r="W51" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X51" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y51" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 7 vs RotoWire 9</t>
-        </is>
-      </c>
+      <c r="AB51" t="inlineStr"/>
       <c r="AC51" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -15164,28 +15140,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="W53" t="inlineStr"/>
-      <c r="X53" t="inlineStr"/>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="Y53" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB53" t="inlineStr"/>
       <c r="AC53" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -16328,34 +16308,30 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -18580,34 +18556,30 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -20560,34 +20532,30 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -21402,28 +21370,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="W20" t="inlineStr"/>
-      <c r="X20" t="inlineStr"/>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="Y20" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB20" t="inlineStr"/>
       <c r="AC20" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
